--- a/src/converted/users.xlsx
+++ b/src/converted/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -417,263 +417,42 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
       <c r="B2" t="str">
-        <v>afa</v>
+        <v>Zeuser</v>
       </c>
       <c r="C2" t="str">
-        <v>eef</v>
+        <v>balandinkiril2008@yandex.ru</v>
       </c>
       <c r="D2" t="str">
-        <v>43</v>
+        <v>89585732912</v>
       </c>
       <c r="E2" t="str">
-        <v>sds</v>
+        <v>Недвижимость</v>
       </c>
     </row>
     <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
       <c r="B3" t="str">
-        <v>afa</v>
+        <v>Zeuser</v>
       </c>
       <c r="C3" t="str">
-        <v>eef</v>
+        <v>balandinkiril2008@yandex.ru</v>
       </c>
       <c r="D3" t="str">
-        <v>43</v>
+        <v>89585732912</v>
       </c>
       <c r="E3" t="str">
-        <v>sds</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="str">
-        <v>afa</v>
-      </c>
-      <c r="C4" t="str">
-        <v>eef</v>
-      </c>
-      <c r="D4" t="str">
-        <v>43</v>
-      </c>
-      <c r="E4" t="str">
-        <v>sds</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="str">
-        <v>afa</v>
-      </c>
-      <c r="C5" t="str">
-        <v>eef</v>
-      </c>
-      <c r="D5" t="str">
-        <v>43</v>
-      </c>
-      <c r="E5" t="str">
-        <v>sds</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="str">
-        <v>afa</v>
-      </c>
-      <c r="C6" t="str">
-        <v>eef</v>
-      </c>
-      <c r="D6" t="str">
-        <v>43</v>
-      </c>
-      <c r="E6" t="str">
-        <v>sds</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="str">
-        <v>afa</v>
-      </c>
-      <c r="C7" t="str">
-        <v>eef</v>
-      </c>
-      <c r="D7" t="str">
-        <v>43</v>
-      </c>
-      <c r="E7" t="str">
-        <v>sds</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E8" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E9" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E10" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E11" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E12" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E13" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E14" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E15" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E16" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E17" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E18" t="str">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Add your name in the body</v>
-      </c>
-      <c r="E19" t="str">
-        <v>433</v>
+        <v>Товары</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/converted/users.xlsx
+++ b/src/converted/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,41 +418,24 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Zeuser</v>
+        <v>Add your name in the body</v>
       </c>
       <c r="C2" t="str">
-        <v>balandinkiril2008@yandex.ru</v>
+        <v>Add your name in the body</v>
       </c>
       <c r="D2" t="str">
-        <v>89585732912</v>
+        <v>Add your name in the body</v>
       </c>
       <c r="E2" t="str">
-        <v>Недвижимость</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Zeuser</v>
-      </c>
-      <c r="C3" t="str">
-        <v>balandinkiril2008@yandex.ru</v>
-      </c>
-      <c r="D3" t="str">
-        <v>89585732912</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Товары</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>